--- a/conformance/fixtures/006-filename-forbidden-chars/template.xlsx
+++ b/conformance/fixtures/006-filename-forbidden-chars/template.xlsx
@@ -26,7 +26,7 @@
     <t>Data</t>
   </si>
   <si>
-    <t>header_row</t>
+    <t>source_table</t>
   </si>
   <si>
     <t>1</t>
@@ -455,7 +455,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -476,6 +476,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/conformance/fixtures/006-filename-forbidden-chars/template.xlsx
+++ b/conformance/fixtures/006-filename-forbidden-chars/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
     <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -455,7 +455,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -476,6 +476,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>